--- a/Validation/multi-licensing_relationship_classification.xlsx
+++ b/Validation/multi-licensing_relationship_classification.xlsx
@@ -2287,6 +2287,7 @@
   <dimension ref="A1:F240"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
+    <col min="3" max="3" width="30.45" customWidth="1"/>
     <col min="4" max="5" width="15.3166666666667" customWidth="1"/>
     <col min="6" max="6" width="14.45" customWidth="1"/>
   </cols>
